--- a/Economic modelling/Annual_negative_impacts.xlsx
+++ b/Economic modelling/Annual_negative_impacts.xlsx
@@ -423,7 +423,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>2022</v>
@@ -440,7 +440,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>2009</v>
@@ -457,7 +457,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>2014</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>2021</v>
@@ -483,7 +483,7 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>-0.6931963523331055</v>
+        <v>-0.2129252661251299</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>2008</v>
@@ -508,7 +508,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>2011</v>
@@ -517,7 +517,7 @@
         <v>4</v>
       </c>
       <c r="D7">
-        <v>-0.5489419357601031</v>
+        <v>-0.6192689761511815</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>2015</v>
@@ -542,7 +542,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>2007</v>
@@ -559,7 +559,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>2020</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <v>2016</v>
@@ -593,7 +593,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B12">
         <v>2010</v>
@@ -602,7 +602,7 @@
         <v>4</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>-0.06445466473074821</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -610,7 +610,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B13">
         <v>2006</v>
@@ -627,7 +627,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>2017</v>
@@ -644,7 +644,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>2019</v>
@@ -661,7 +661,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B16">
         <v>2012</v>
@@ -678,7 +678,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>2005</v>
@@ -695,7 +695,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="B18">
         <v>2018</v>
@@ -704,7 +704,7 @@
         <v>4</v>
       </c>
       <c r="D18">
-        <v>-2.599742709168237</v>
+        <v>-2.410533537249654</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -712,7 +712,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B19">
         <v>2013</v>
@@ -729,7 +729,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="B20">
         <v>2013</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="B21">
         <v>2015</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B22">
         <v>2014</v>
@@ -780,7 +780,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="B23">
         <v>2020</v>
@@ -797,7 +797,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="B24">
         <v>2016</v>
@@ -814,7 +814,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="B25">
         <v>2017</v>
@@ -831,7 +831,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="B26">
         <v>2018</v>
@@ -848,7 +848,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B27">
         <v>2012</v>
@@ -865,7 +865,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="B28">
         <v>2019</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29">
         <v>2011</v>
@@ -891,7 +891,7 @@
         <v>5</v>
       </c>
       <c r="D29">
-        <v>-0.03414108216453906</v>
+        <v>-0.04694398797624121</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -899,7 +899,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="B30">
         <v>2005</v>
@@ -916,7 +916,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B31">
         <v>2022</v>
@@ -933,7 +933,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B32">
         <v>2010</v>
@@ -950,7 +950,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="B33">
         <v>2006</v>
@@ -959,7 +959,7 @@
         <v>5</v>
       </c>
       <c r="D33">
-        <v>-0.01906918117777495</v>
+        <v>-0.09961378792356218</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="B34">
         <v>2021</v>
@@ -976,7 +976,7 @@
         <v>5</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>-0.02956055550675215</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -984,7 +984,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B35">
         <v>2009</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B36">
         <v>2008</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="B37">
         <v>2007</v>
@@ -1035,7 +1035,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="B38">
         <v>2020</v>
@@ -1052,7 +1052,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B39">
         <v>2018</v>
@@ -1061,7 +1061,7 @@
         <v>6</v>
       </c>
       <c r="D39">
-        <v>-8.00374780999657</v>
+        <v>-5.332798334315116</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -1069,7 +1069,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B40">
         <v>2006</v>
@@ -1086,7 +1086,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="B41">
         <v>2022</v>
@@ -1095,7 +1095,7 @@
         <v>6</v>
       </c>
       <c r="D41">
-        <v>-0.3176955423048199</v>
+        <v>-0.1381467775441229</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B42">
         <v>2017</v>
@@ -1120,7 +1120,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B43">
         <v>2007</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B44">
         <v>2016</v>
@@ -1146,7 +1146,7 @@
         <v>6</v>
       </c>
       <c r="D44">
-        <v>-0.01265206950270217</v>
+        <v>-0.004343195068597685</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B45">
         <v>2008</v>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B46">
         <v>2019</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B47">
         <v>2015</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="B48">
         <v>2009</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="1">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B49">
         <v>2014</v>
@@ -1231,7 +1231,7 @@
         <v>6</v>
       </c>
       <c r="D49">
-        <v>-0.01606648283081328</v>
+        <v>0</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="1">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="B50">
         <v>2005</v>
@@ -1256,7 +1256,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="1">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="B51">
         <v>2010</v>
@@ -1273,7 +1273,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="B52">
         <v>2013</v>
@@ -1282,7 +1282,7 @@
         <v>6</v>
       </c>
       <c r="D52">
-        <v>-2.496955468987818</v>
+        <v>-0.6219457263897877</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -1290,7 +1290,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B53">
         <v>2021</v>
@@ -1307,7 +1307,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="1">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="B54">
         <v>2011</v>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="1">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="B55">
         <v>2012</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="1">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B56">
         <v>2022</v>
@@ -1350,7 +1350,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>-0.3176955423048199</v>
+        <v>-0.1381467775441229</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -1358,7 +1358,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="1">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B57">
         <v>2020</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="1">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B58">
         <v>2021</v>
@@ -1384,7 +1384,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>-0.6931963523331055</v>
+        <v>-0.2424858216318821</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -1392,7 +1392,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="1">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="B59">
         <v>2005</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="1">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B60">
         <v>2019</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="1">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B61">
         <v>2018</v>
@@ -1435,7 +1435,7 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>-9.844521880674115</v>
+        <v>-7.285889021840912</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="1">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B62">
         <v>2017</v>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="1">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B63">
         <v>2016</v>
@@ -1469,7 +1469,7 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>-0.01265206950270217</v>
+        <v>-0.004343195068597685</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="1">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B64">
         <v>2015</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="1">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B65">
         <v>2013</v>
@@ -1503,7 +1503,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>-2.528990898256237</v>
+        <v>-0.6539811556582076</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -1511,7 +1511,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="1">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="B66">
         <v>2012</v>
@@ -1528,7 +1528,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="1">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="B67">
         <v>2011</v>
@@ -1537,7 +1537,7 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>-0.7149549050182498</v>
+        <v>-0.7980848512210305</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="1">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="B68">
         <v>2010</v>
@@ -1554,7 +1554,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>-0.06445466473074821</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="1">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="B69">
         <v>2009</v>
@@ -1579,7 +1579,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="1">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="B70">
         <v>2008</v>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="1">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="B71">
         <v>2007</v>
@@ -1613,7 +1613,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="1">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="B72">
         <v>2006</v>
@@ -1622,7 +1622,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>-0.01906918117777495</v>
+        <v>-0.09961378792356218</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="1">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="B73">
         <v>2014</v>
@@ -1639,7 +1639,7 @@
         <v>7</v>
       </c>
       <c r="D73">
-        <v>-0.01606648283081328</v>
+        <v>0</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B74">
         <v>2022</v>
@@ -1664,7 +1664,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="1">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="B75">
         <v>2009</v>
@@ -1681,7 +1681,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="1">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="B76">
         <v>2014</v>
@@ -1690,7 +1690,7 @@
         <v>4</v>
       </c>
       <c r="D76">
-        <v>-0.5199517956523073</v>
+        <v>-0.7497210432719079</v>
       </c>
       <c r="E76" t="s">
         <v>9</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="1">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B77">
         <v>2021</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="1">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="B78">
         <v>2008</v>
@@ -1732,7 +1732,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="1">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="B79">
         <v>2011</v>
@@ -1749,7 +1749,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="1">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="B80">
         <v>2015</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="1">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="B81">
         <v>2007</v>
@@ -1783,7 +1783,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="1">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="B82">
         <v>2020</v>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="1">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="B83">
         <v>2016</v>
@@ -1817,7 +1817,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="1">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="B84">
         <v>2010</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="1">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="B85">
         <v>2006</v>
@@ -1843,7 +1843,7 @@
         <v>4</v>
       </c>
       <c r="D85">
-        <v>-1.356530544610653</v>
+        <v>-1.46869796931746</v>
       </c>
       <c r="E85" t="s">
         <v>9</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="1">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="B86">
         <v>2017</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="1">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="B87">
         <v>2019</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="1">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="B88">
         <v>2012</v>
@@ -1902,7 +1902,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="1">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="B89">
         <v>2005</v>
@@ -1919,7 +1919,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="1">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="B90">
         <v>2018</v>
@@ -1928,7 +1928,7 @@
         <v>4</v>
       </c>
       <c r="D90">
-        <v>-0.7569260707417055</v>
+        <v>-0.5146173227165936</v>
       </c>
       <c r="E90" t="s">
         <v>9</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="1">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="B91">
         <v>2013</v>
@@ -1945,7 +1945,7 @@
         <v>4</v>
       </c>
       <c r="D91">
-        <v>-0.445873407706699</v>
+        <v>-0.3609740974516575</v>
       </c>
       <c r="E91" t="s">
         <v>9</v>
@@ -1953,7 +1953,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="1">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="B92">
         <v>2013</v>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="1">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="B93">
         <v>2015</v>
@@ -1987,7 +1987,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="1">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="B94">
         <v>2014</v>
@@ -2004,7 +2004,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="1">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="B95">
         <v>2020</v>
@@ -2021,7 +2021,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="1">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="B96">
         <v>2016</v>
@@ -2038,7 +2038,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="1">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="B97">
         <v>2017</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="1">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="B98">
         <v>2018</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="1">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="B99">
         <v>2012</v>
@@ -2089,7 +2089,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="1">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="B100">
         <v>2019</v>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="1">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="B101">
         <v>2011</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="1">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="B102">
         <v>2005</v>
@@ -2140,7 +2140,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="1">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="B103">
         <v>2022</v>
@@ -2157,7 +2157,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="1">
-        <v>22</v>
+        <v>102</v>
       </c>
       <c r="B104">
         <v>2010</v>
@@ -2174,7 +2174,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="1">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="B105">
         <v>2006</v>
@@ -2183,7 +2183,7 @@
         <v>5</v>
       </c>
       <c r="D105">
-        <v>-0.083702187264456</v>
+        <v>-0.02179438330797836</v>
       </c>
       <c r="E105" t="s">
         <v>9</v>
@@ -2191,7 +2191,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="1">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="B106">
         <v>2021</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="1">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="B107">
         <v>2009</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="1">
-        <v>14</v>
+        <v>106</v>
       </c>
       <c r="B108">
         <v>2008</v>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="1">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="B109">
         <v>2007</v>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="1">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="B110">
         <v>2020</v>
@@ -2268,7 +2268,7 @@
         <v>6</v>
       </c>
       <c r="D110">
-        <v>-0.08302297510336054</v>
+        <v>0</v>
       </c>
       <c r="E110" t="s">
         <v>9</v>
@@ -2276,7 +2276,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="1">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="B111">
         <v>2018</v>
@@ -2285,7 +2285,7 @@
         <v>6</v>
       </c>
       <c r="D111">
-        <v>-9.941708799832286</v>
+        <v>-8.126279537892605</v>
       </c>
       <c r="E111" t="s">
         <v>9</v>
@@ -2293,7 +2293,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="1">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="B112">
         <v>2006</v>
@@ -2302,7 +2302,7 @@
         <v>6</v>
       </c>
       <c r="D112">
-        <v>-2.458211007952845</v>
+        <v>-2.328074945466622</v>
       </c>
       <c r="E112" t="s">
         <v>9</v>
@@ -2310,7 +2310,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="1">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="B113">
         <v>2022</v>
@@ -2319,7 +2319,7 @@
         <v>6</v>
       </c>
       <c r="D113">
-        <v>-9.635932799666787</v>
+        <v>-8.276590009366021</v>
       </c>
       <c r="E113" t="s">
         <v>9</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="1">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="B114">
         <v>2017</v>
@@ -2336,7 +2336,7 @@
         <v>6</v>
       </c>
       <c r="D114">
-        <v>-3.585607063131536</v>
+        <v>-3.344905385019417</v>
       </c>
       <c r="E114" t="s">
         <v>9</v>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="1">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="B115">
         <v>2007</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="1">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="B116">
         <v>2016</v>
@@ -2370,7 +2370,7 @@
         <v>6</v>
       </c>
       <c r="D116">
-        <v>-5.700418312956623</v>
+        <v>-4.641907340797494</v>
       </c>
       <c r="E116" t="s">
         <v>9</v>
@@ -2378,7 +2378,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="1">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="B117">
         <v>2008</v>
@@ -2395,7 +2395,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="1">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="B118">
         <v>2019</v>
@@ -2404,7 +2404,7 @@
         <v>6</v>
       </c>
       <c r="D118">
-        <v>-1.186988003399285</v>
+        <v>-1.196638312370011</v>
       </c>
       <c r="E118" t="s">
         <v>9</v>
@@ -2412,7 +2412,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="1">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="B119">
         <v>2015</v>
@@ -2429,7 +2429,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="1">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="B120">
         <v>2009</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="1">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="B121">
         <v>2014</v>
@@ -2455,7 +2455,7 @@
         <v>6</v>
       </c>
       <c r="D121">
-        <v>-0.7909705984122501</v>
+        <v>-0.9496770388082161</v>
       </c>
       <c r="E121" t="s">
         <v>9</v>
@@ -2463,7 +2463,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="1">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="B122">
         <v>2005</v>
@@ -2480,7 +2480,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="1">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="B123">
         <v>2010</v>
@@ -2497,7 +2497,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="1">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="B124">
         <v>2013</v>
@@ -2506,7 +2506,7 @@
         <v>6</v>
       </c>
       <c r="D124">
-        <v>-6.832964233018668</v>
+        <v>-6.40842354478549</v>
       </c>
       <c r="E124" t="s">
         <v>9</v>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="1">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="B125">
         <v>2021</v>
@@ -2531,7 +2531,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="1">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="B126">
         <v>2011</v>
@@ -2540,7 +2540,7 @@
         <v>6</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>-0.0204583810373023</v>
       </c>
       <c r="E126" t="s">
         <v>9</v>
@@ -2548,7 +2548,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="1">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="B127">
         <v>2012</v>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="1">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="B128">
         <v>2022</v>
@@ -2574,7 +2574,7 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>-9.844728280478373</v>
+        <v>-8.485385490177604</v>
       </c>
       <c r="E128" t="s">
         <v>9</v>
@@ -2582,7 +2582,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="1">
-        <v>60</v>
+        <v>127</v>
       </c>
       <c r="B129">
         <v>2020</v>
@@ -2591,7 +2591,7 @@
         <v>7</v>
       </c>
       <c r="D129">
-        <v>-0.08302297510336054</v>
+        <v>0</v>
       </c>
       <c r="E129" t="s">
         <v>9</v>
@@ -2599,7 +2599,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="1">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="B130">
         <v>2021</v>
@@ -2616,7 +2616,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="1">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="B131">
         <v>2005</v>
@@ -2633,7 +2633,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="1">
-        <v>56</v>
+        <v>130</v>
       </c>
       <c r="B132">
         <v>2019</v>
@@ -2650,7 +2650,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="1">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="B133">
         <v>2018</v>
@@ -2659,7 +2659,7 @@
         <v>7</v>
       </c>
       <c r="D133">
-        <v>-10.52064093094238</v>
+        <v>-8.321338022102017</v>
       </c>
       <c r="E133" t="s">
         <v>9</v>
@@ -2667,7 +2667,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="1">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="B134">
         <v>2017</v>
@@ -2676,7 +2676,7 @@
         <v>7</v>
       </c>
       <c r="D134">
-        <v>-3.585607063131536</v>
+        <v>-3.344905385019417</v>
       </c>
       <c r="E134" t="s">
         <v>9</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="1">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="B135">
         <v>2016</v>
@@ -2693,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="D135">
-        <v>-5.843763031248028</v>
+        <v>-4.785252059088899</v>
       </c>
       <c r="E135" t="s">
         <v>9</v>
@@ -2701,7 +2701,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="1">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="B136">
         <v>2015</v>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="1">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="B137">
         <v>2013</v>
@@ -2727,7 +2727,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>-7.278837640725366</v>
+        <v>-6.769397642237148</v>
       </c>
       <c r="E137" t="s">
         <v>9</v>
@@ -2735,7 +2735,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="1">
-        <v>28</v>
+        <v>136</v>
       </c>
       <c r="B138">
         <v>2012</v>
@@ -2752,7 +2752,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="1">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="B139">
         <v>2011</v>
@@ -2761,7 +2761,7 @@
         <v>7</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>-0.0204583810373023</v>
       </c>
       <c r="E139" t="s">
         <v>9</v>
@@ -2769,7 +2769,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="1">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="B140">
         <v>2010</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="1">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="B141">
         <v>2009</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="1">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="B142">
         <v>2008</v>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="1">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="B143">
         <v>2007</v>
@@ -2837,7 +2837,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="1">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="B144">
         <v>2006</v>
@@ -2846,7 +2846,7 @@
         <v>7</v>
       </c>
       <c r="D144">
-        <v>-2.885234864983521</v>
+        <v>-2.851118142791655</v>
       </c>
       <c r="E144" t="s">
         <v>9</v>
@@ -2854,7 +2854,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="1">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="B145">
         <v>2014</v>
@@ -2863,7 +2863,7 @@
         <v>7</v>
       </c>
       <c r="D145">
-        <v>-1.165315783741656</v>
+        <v>-1.553791471757223</v>
       </c>
       <c r="E145" t="s">
         <v>9</v>
@@ -2871,7 +2871,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="1">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="B146">
         <v>2022</v>
@@ -2880,7 +2880,7 @@
         <v>4</v>
       </c>
       <c r="D146">
-        <v>-0.3291736359188365</v>
+        <v>-0.1665076770136946</v>
       </c>
       <c r="E146" t="s">
         <v>10</v>
@@ -2888,7 +2888,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="1">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="B147">
         <v>2009</v>
@@ -2905,7 +2905,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="1">
-        <v>39</v>
+        <v>146</v>
       </c>
       <c r="B148">
         <v>2014</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="1">
-        <v>67</v>
+        <v>147</v>
       </c>
       <c r="B149">
         <v>2021</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="1">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="B150">
         <v>2008</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="1">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="B151">
         <v>2011</v>
@@ -2965,7 +2965,7 @@
         <v>4</v>
       </c>
       <c r="D151">
-        <v>-0.3317180321350691</v>
+        <v>-0.03030159848419754</v>
       </c>
       <c r="E151" t="s">
         <v>10</v>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="1">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="B152">
         <v>2015</v>
@@ -2982,7 +2982,7 @@
         <v>4</v>
       </c>
       <c r="D152">
-        <v>-0.3834631206726756</v>
+        <v>-0.2231968599823196</v>
       </c>
       <c r="E152" t="s">
         <v>10</v>
@@ -2990,7 +2990,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="1">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="B153">
         <v>2007</v>
@@ -2999,7 +2999,7 @@
         <v>4</v>
       </c>
       <c r="D153">
-        <v>-1.94859095813082</v>
+        <v>-1.312966207456929</v>
       </c>
       <c r="E153" t="s">
         <v>10</v>
@@ -3007,7 +3007,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="1">
-        <v>63</v>
+        <v>152</v>
       </c>
       <c r="B154">
         <v>2020</v>
@@ -3016,7 +3016,7 @@
         <v>4</v>
       </c>
       <c r="D154">
-        <v>-0.2496856559473044</v>
+        <v>-0.1193699810409606</v>
       </c>
       <c r="E154" t="s">
         <v>10</v>
@@ -3024,7 +3024,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="1">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="B155">
         <v>2016</v>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="1">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="B156">
         <v>2010</v>
@@ -3058,7 +3058,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="1">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="B157">
         <v>2006</v>
@@ -3067,7 +3067,7 @@
         <v>4</v>
       </c>
       <c r="D157">
-        <v>-1.577889954172759</v>
+        <v>-0.5490899741844123</v>
       </c>
       <c r="E157" t="s">
         <v>10</v>
@@ -3075,7 +3075,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="1">
-        <v>51</v>
+        <v>156</v>
       </c>
       <c r="B158">
         <v>2017</v>
@@ -3092,7 +3092,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="1">
-        <v>59</v>
+        <v>157</v>
       </c>
       <c r="B159">
         <v>2019</v>
@@ -3101,7 +3101,7 @@
         <v>4</v>
       </c>
       <c r="D159">
-        <v>-0.008765522279034906</v>
+        <v>0</v>
       </c>
       <c r="E159" t="s">
         <v>10</v>
@@ -3109,7 +3109,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="1">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="B160">
         <v>2012</v>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="1">
-        <v>3</v>
+        <v>159</v>
       </c>
       <c r="B161">
         <v>2005</v>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="1">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="B162">
         <v>2018</v>
@@ -3152,7 +3152,7 @@
         <v>4</v>
       </c>
       <c r="D162">
-        <v>-1.024183752369502</v>
+        <v>-0.7163319078271659</v>
       </c>
       <c r="E162" t="s">
         <v>10</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="1">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="B163">
         <v>2013</v>
@@ -3169,7 +3169,7 @@
         <v>4</v>
       </c>
       <c r="D163">
-        <v>-0.1627552678356787</v>
+        <v>-0.08737580847272636</v>
       </c>
       <c r="E163" t="s">
         <v>10</v>
@@ -3177,7 +3177,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="1">
-        <v>34</v>
+        <v>162</v>
       </c>
       <c r="B164">
         <v>2013</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="1">
-        <v>42</v>
+        <v>163</v>
       </c>
       <c r="B165">
         <v>2015</v>
@@ -3211,7 +3211,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="1">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="B166">
         <v>2014</v>
@@ -3228,7 +3228,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="1">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="B167">
         <v>2020</v>
@@ -3245,7 +3245,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="1">
-        <v>46</v>
+        <v>166</v>
       </c>
       <c r="B168">
         <v>2016</v>
@@ -3262,7 +3262,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="1">
-        <v>50</v>
+        <v>167</v>
       </c>
       <c r="B169">
         <v>2017</v>
@@ -3279,7 +3279,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="1">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="B170">
         <v>2018</v>
@@ -3296,7 +3296,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="1">
-        <v>30</v>
+        <v>169</v>
       </c>
       <c r="B171">
         <v>2012</v>
@@ -3313,7 +3313,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="1">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="B172">
         <v>2019</v>
@@ -3330,7 +3330,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="1">
-        <v>26</v>
+        <v>171</v>
       </c>
       <c r="B173">
         <v>2011</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="1">
-        <v>2</v>
+        <v>172</v>
       </c>
       <c r="B174">
         <v>2005</v>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="1">
-        <v>70</v>
+        <v>173</v>
       </c>
       <c r="B175">
         <v>2022</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="1">
-        <v>22</v>
+        <v>174</v>
       </c>
       <c r="B176">
         <v>2010</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="1">
-        <v>6</v>
+        <v>175</v>
       </c>
       <c r="B177">
         <v>2006</v>
@@ -3415,7 +3415,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="1">
-        <v>66</v>
+        <v>176</v>
       </c>
       <c r="B178">
         <v>2021</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="1">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="B179">
         <v>2009</v>
@@ -3449,7 +3449,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="1">
-        <v>14</v>
+        <v>178</v>
       </c>
       <c r="B180">
         <v>2008</v>
@@ -3466,7 +3466,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="1">
-        <v>10</v>
+        <v>179</v>
       </c>
       <c r="B181">
         <v>2007</v>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="1">
-        <v>61</v>
+        <v>180</v>
       </c>
       <c r="B182">
         <v>2020</v>
@@ -3500,7 +3500,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="1">
-        <v>53</v>
+        <v>181</v>
       </c>
       <c r="B183">
         <v>2018</v>
@@ -3509,7 +3509,7 @@
         <v>6</v>
       </c>
       <c r="D183">
-        <v>-1.976890238383904</v>
+        <v>-1.320210607723436</v>
       </c>
       <c r="E183" t="s">
         <v>10</v>
@@ -3517,7 +3517,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="1">
-        <v>5</v>
+        <v>182</v>
       </c>
       <c r="B184">
         <v>2006</v>
@@ -3526,7 +3526,7 @@
         <v>6</v>
       </c>
       <c r="D184">
-        <v>-1.379659154281959</v>
+        <v>-0.9772271601703137</v>
       </c>
       <c r="E184" t="s">
         <v>10</v>
@@ -3534,7 +3534,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="1">
-        <v>69</v>
+        <v>183</v>
       </c>
       <c r="B185">
         <v>2022</v>
@@ -3543,7 +3543,7 @@
         <v>6</v>
       </c>
       <c r="D185">
-        <v>-5.251245376052258</v>
+        <v>-3.31541379394207</v>
       </c>
       <c r="E185" t="s">
         <v>10</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="1">
-        <v>49</v>
+        <v>184</v>
       </c>
       <c r="B186">
         <v>2017</v>
@@ -3560,7 +3560,7 @@
         <v>6</v>
       </c>
       <c r="D186">
-        <v>-1.611047845879096</v>
+        <v>-1.617980807293224</v>
       </c>
       <c r="E186" t="s">
         <v>10</v>
@@ -3568,7 +3568,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="1">
-        <v>9</v>
+        <v>185</v>
       </c>
       <c r="B187">
         <v>2007</v>
@@ -3577,7 +3577,7 @@
         <v>6</v>
       </c>
       <c r="D187">
-        <v>-1.325138761682202</v>
+        <v>-1.011488677048495</v>
       </c>
       <c r="E187" t="s">
         <v>10</v>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="1">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="B188">
         <v>2016</v>
@@ -3594,7 +3594,7 @@
         <v>6</v>
       </c>
       <c r="D188">
-        <v>-2.241937347099847</v>
+        <v>-1.907878884698577</v>
       </c>
       <c r="E188" t="s">
         <v>10</v>
@@ -3602,7 +3602,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="1">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="B189">
         <v>2008</v>
@@ -3619,7 +3619,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="1">
-        <v>57</v>
+        <v>188</v>
       </c>
       <c r="B190">
         <v>2019</v>
@@ -3628,7 +3628,7 @@
         <v>6</v>
       </c>
       <c r="D190">
-        <v>-0.8034150811673306</v>
+        <v>-0.531772663317113</v>
       </c>
       <c r="E190" t="s">
         <v>10</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="1">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="B191">
         <v>2015</v>
@@ -3653,7 +3653,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="1">
-        <v>17</v>
+        <v>190</v>
       </c>
       <c r="B192">
         <v>2009</v>
@@ -3662,7 +3662,7 @@
         <v>6</v>
       </c>
       <c r="D192">
-        <v>-0.03926339770070737</v>
+        <v>0</v>
       </c>
       <c r="E192" t="s">
         <v>10</v>
@@ -3670,7 +3670,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="1">
-        <v>37</v>
+        <v>191</v>
       </c>
       <c r="B193">
         <v>2014</v>
@@ -3679,7 +3679,7 @@
         <v>6</v>
       </c>
       <c r="D193">
-        <v>-0.08898458473444977</v>
+        <v>-0.1458830448447509</v>
       </c>
       <c r="E193" t="s">
         <v>10</v>
@@ -3687,7 +3687,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="1">
-        <v>1</v>
+        <v>192</v>
       </c>
       <c r="B194">
         <v>2005</v>
@@ -3696,7 +3696,7 @@
         <v>6</v>
       </c>
       <c r="D194">
-        <v>-0.1594780672543854</v>
+        <v>-0.04287681679660359</v>
       </c>
       <c r="E194" t="s">
         <v>10</v>
@@ -3704,7 +3704,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="1">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="B195">
         <v>2010</v>
@@ -3721,7 +3721,7 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="1">
-        <v>33</v>
+        <v>194</v>
       </c>
       <c r="B196">
         <v>2013</v>
@@ -3730,7 +3730,7 @@
         <v>6</v>
       </c>
       <c r="D196">
-        <v>-3.157894027930607</v>
+        <v>-2.449391753664354</v>
       </c>
       <c r="E196" t="s">
         <v>10</v>
@@ -3738,7 +3738,7 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="1">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="B197">
         <v>2021</v>
@@ -3755,7 +3755,7 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="1">
-        <v>25</v>
+        <v>196</v>
       </c>
       <c r="B198">
         <v>2011</v>
@@ -3764,7 +3764,7 @@
         <v>6</v>
       </c>
       <c r="D198">
-        <v>-0.3274267306086844</v>
+        <v>-0.1306837315268894</v>
       </c>
       <c r="E198" t="s">
         <v>10</v>
@@ -3772,7 +3772,7 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="1">
-        <v>29</v>
+        <v>197</v>
       </c>
       <c r="B199">
         <v>2012</v>
@@ -3789,7 +3789,7 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="1">
-        <v>68</v>
+        <v>198</v>
       </c>
       <c r="B200">
         <v>2022</v>
@@ -3798,7 +3798,7 @@
         <v>7</v>
       </c>
       <c r="D200">
-        <v>-5.580419011971094</v>
+        <v>-3.481921470955764</v>
       </c>
       <c r="E200" t="s">
         <v>10</v>
@@ -3806,7 +3806,7 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="1">
-        <v>60</v>
+        <v>199</v>
       </c>
       <c r="B201">
         <v>2020</v>
@@ -3815,7 +3815,7 @@
         <v>7</v>
       </c>
       <c r="D201">
-        <v>-0.2496856559473044</v>
+        <v>-0.1193699810409606</v>
       </c>
       <c r="E201" t="s">
         <v>10</v>
@@ -3823,7 +3823,7 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="1">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="B202">
         <v>2021</v>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="1">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="B203">
         <v>2005</v>
@@ -3849,7 +3849,7 @@
         <v>7</v>
       </c>
       <c r="D203">
-        <v>-0.1594780672543854</v>
+        <v>-0.04287681679660359</v>
       </c>
       <c r="E203" t="s">
         <v>10</v>
@@ -3857,7 +3857,7 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="1">
-        <v>56</v>
+        <v>202</v>
       </c>
       <c r="B204">
         <v>2019</v>
@@ -3866,7 +3866,7 @@
         <v>7</v>
       </c>
       <c r="D204">
-        <v>-0.8121806034463654</v>
+        <v>-0.531772663317113</v>
       </c>
       <c r="E204" t="s">
         <v>10</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="1">
-        <v>52</v>
+        <v>203</v>
       </c>
       <c r="B205">
         <v>2018</v>
@@ -3883,7 +3883,7 @@
         <v>7</v>
       </c>
       <c r="D205">
-        <v>-2.836519837244672</v>
+        <v>-2.036542515550602</v>
       </c>
       <c r="E205" t="s">
         <v>10</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="1">
-        <v>48</v>
+        <v>204</v>
       </c>
       <c r="B206">
         <v>2017</v>
@@ -3900,7 +3900,7 @@
         <v>7</v>
       </c>
       <c r="D206">
-        <v>-1.611047845879096</v>
+        <v>-1.617980807293224</v>
       </c>
       <c r="E206" t="s">
         <v>10</v>
@@ -3908,7 +3908,7 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="1">
-        <v>44</v>
+        <v>205</v>
       </c>
       <c r="B207">
         <v>2016</v>
@@ -3917,7 +3917,7 @@
         <v>7</v>
       </c>
       <c r="D207">
-        <v>-2.316496558588796</v>
+        <v>-1.982438096187525</v>
       </c>
       <c r="E207" t="s">
         <v>10</v>
@@ -3925,7 +3925,7 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="1">
-        <v>40</v>
+        <v>206</v>
       </c>
       <c r="B208">
         <v>2015</v>
@@ -3934,7 +3934,7 @@
         <v>7</v>
       </c>
       <c r="D208">
-        <v>-0.3834631206726756</v>
+        <v>-0.2231968599823196</v>
       </c>
       <c r="E208" t="s">
         <v>10</v>
@@ -3942,7 +3942,7 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="1">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="B209">
         <v>2013</v>
@@ -3951,7 +3951,7 @@
         <v>7</v>
       </c>
       <c r="D209">
-        <v>-3.320649295766285</v>
+        <v>-2.536767562137081</v>
       </c>
       <c r="E209" t="s">
         <v>10</v>
@@ -3959,7 +3959,7 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="1">
-        <v>28</v>
+        <v>208</v>
       </c>
       <c r="B210">
         <v>2012</v>
@@ -3976,7 +3976,7 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="1">
-        <v>24</v>
+        <v>209</v>
       </c>
       <c r="B211">
         <v>2011</v>
@@ -3985,7 +3985,7 @@
         <v>7</v>
       </c>
       <c r="D211">
-        <v>-0.4624017636619586</v>
+        <v>-0.1609853300110869</v>
       </c>
       <c r="E211" t="s">
         <v>10</v>
@@ -3993,7 +3993,7 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="1">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="B212">
         <v>2010</v>
@@ -4010,7 +4010,7 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="1">
-        <v>16</v>
+        <v>211</v>
       </c>
       <c r="B213">
         <v>2009</v>
@@ -4019,7 +4019,7 @@
         <v>7</v>
       </c>
       <c r="D213">
-        <v>-0.04150988217600174</v>
+        <v>-0.002246484475294376</v>
       </c>
       <c r="E213" t="s">
         <v>10</v>
@@ -4027,7 +4027,7 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="1">
-        <v>12</v>
+        <v>212</v>
       </c>
       <c r="B214">
         <v>2008</v>
@@ -4044,7 +4044,7 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="1">
-        <v>8</v>
+        <v>213</v>
       </c>
       <c r="B215">
         <v>2007</v>
@@ -4053,7 +4053,7 @@
         <v>7</v>
       </c>
       <c r="D215">
-        <v>-3.273729719813022</v>
+        <v>-2.324454884505424</v>
       </c>
       <c r="E215" t="s">
         <v>10</v>
@@ -4061,7 +4061,7 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="1">
-        <v>4</v>
+        <v>214</v>
       </c>
       <c r="B216">
         <v>2006</v>
@@ -4070,7 +4070,7 @@
         <v>7</v>
       </c>
       <c r="D216">
-        <v>-2.516369582488522</v>
+        <v>-1.30999779838602</v>
       </c>
       <c r="E216" t="s">
         <v>10</v>
@@ -4078,7 +4078,7 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="1">
-        <v>36</v>
+        <v>215</v>
       </c>
       <c r="B217">
         <v>2014</v>

--- a/Economic modelling/Annual_negative_impacts.xlsx
+++ b/Economic modelling/Annual_negative_impacts.xlsx
@@ -432,7 +432,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.1689888354892385</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -449,7 +449,7 @@
         <v>4</v>
       </c>
       <c r="D3">
-        <v>-0.03766243654744143</v>
+        <v>-0.2419970624508795</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -483,7 +483,7 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>-0.2129252661251299</v>
+        <v>-5.107611783473442</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -500,7 +500,7 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>-0.454805249099036</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -517,7 +517,7 @@
         <v>4</v>
       </c>
       <c r="D7">
-        <v>-0.6192689761511815</v>
+        <v>-3.836815353859162</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>-0.05435629220570694</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -585,7 +585,7 @@
         <v>4</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>-0.1991465463589419</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -602,7 +602,7 @@
         <v>4</v>
       </c>
       <c r="D12">
-        <v>-0.06445466473074821</v>
+        <v>-4.079522655502504</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -619,7 +619,7 @@
         <v>4</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>-1.566578157512995</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -636,7 +636,7 @@
         <v>4</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>-0.9403546094128435</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -653,7 +653,7 @@
         <v>4</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>-0.3366121291263786</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -670,7 +670,7 @@
         <v>4</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>-0.6789385804232301</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -687,7 +687,7 @@
         <v>4</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>-0.2249373295423551</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -704,7 +704,7 @@
         <v>4</v>
       </c>
       <c r="D18">
-        <v>-2.410533537249654</v>
+        <v>-8.21803097340783</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -721,7 +721,7 @@
         <v>4</v>
       </c>
       <c r="D19">
-        <v>-0.03203542926841986</v>
+        <v>-0.0227448157466243</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -806,7 +806,7 @@
         <v>5</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>-0.02295684756603258</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -857,7 +857,7 @@
         <v>5</v>
       </c>
       <c r="D27">
-        <v>-0.04669088083404113</v>
+        <v>-0.5174301504270004</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -891,7 +891,7 @@
         <v>5</v>
       </c>
       <c r="D29">
-        <v>-0.04694398797624121</v>
+        <v>-0.6401937742179618</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -942,7 +942,7 @@
         <v>5</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>-1.57294422360136</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -959,7 +959,7 @@
         <v>5</v>
       </c>
       <c r="D33">
-        <v>-0.09961378792356218</v>
+        <v>-1.69338115489025</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -976,7 +976,7 @@
         <v>5</v>
       </c>
       <c r="D34">
-        <v>-0.02956055550675215</v>
+        <v>-0.945829949535045</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>-0.6219045674943394</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -1010,7 +1010,7 @@
         <v>5</v>
       </c>
       <c r="D36">
-        <v>-0.08890515369725446</v>
+        <v>-0.3953221659171488</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -1027,7 +1027,7 @@
         <v>5</v>
       </c>
       <c r="D37">
-        <v>-0.1396315562968122</v>
+        <v>-0.04246291415877143</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -1044,7 +1044,7 @@
         <v>6</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>-0.0232457063825476</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -1061,7 +1061,7 @@
         <v>6</v>
       </c>
       <c r="D39">
-        <v>-5.332798334315116</v>
+        <v>-4.239078845029571</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -1078,7 +1078,7 @@
         <v>6</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>-1.120359171877278</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -1095,7 +1095,7 @@
         <v>6</v>
       </c>
       <c r="D41">
-        <v>-0.1381467775441229</v>
+        <v>-0.08937421427802655</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -1146,7 +1146,7 @@
         <v>6</v>
       </c>
       <c r="D44">
-        <v>-0.004343195068597685</v>
+        <v>-0.1648488020793336</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -1163,7 +1163,7 @@
         <v>6</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>-0.01092242000277404</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -1180,7 +1180,7 @@
         <v>6</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>-0.03366349568743462</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -1214,7 +1214,7 @@
         <v>6</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>-0.0471494170859495</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -1265,7 +1265,7 @@
         <v>6</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>-0.2451864516728884</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -1282,7 +1282,7 @@
         <v>6</v>
       </c>
       <c r="D52">
-        <v>-0.6219457263897877</v>
+        <v>-0.009482159099772377</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>-0.6015389048175447</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -1316,7 +1316,7 @@
         <v>6</v>
       </c>
       <c r="D54">
-        <v>-0.1318718870936076</v>
+        <v>-0.2222007555053847</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -1350,7 +1350,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>-0.1381467775441229</v>
+        <v>-0.2222636891519382</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -1367,7 +1367,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>-0.02187356399191111</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -1384,7 +1384,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>-0.2424858216318821</v>
+        <v>-5.486708280856856</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -1401,7 +1401,7 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>-0.1858857098301406</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -1418,7 +1418,7 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>-0.308913840617616</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>-7.285889021840912</v>
+        <v>-10.01730829269766</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -1452,7 +1452,7 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>-0.7770986008342249</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -1469,7 +1469,7 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>-0.004343195068597685</v>
+        <v>-0.2975309019915643</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -1503,7 +1503,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>-0.6539811556582076</v>
+        <v>-0.02771851133241284</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -1520,7 +1520,7 @@
         <v>7</v>
       </c>
       <c r="D66">
-        <v>-0.04669088083404113</v>
+        <v>-0.936811067231289</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -1537,7 +1537,7 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>-0.7980848512210305</v>
+        <v>-3.899831351778564</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -1554,7 +1554,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>-0.06445466473074821</v>
+        <v>-4.794723086186123</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -1571,7 +1571,7 @@
         <v>7</v>
       </c>
       <c r="D69">
-        <v>-0.03766243654744143</v>
+        <v>-0.8446606342257916</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -1588,7 +1588,7 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <v>-0.08890515369725446</v>
+        <v>-0.579594427928548</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -1605,7 +1605,7 @@
         <v>7</v>
       </c>
       <c r="D71">
-        <v>-0.1396315562968122</v>
+        <v>-0.07233010981766083</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -1622,7 +1622,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>-0.09961378792356218</v>
+        <v>-3.519777139631293</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -1656,7 +1656,7 @@
         <v>4</v>
       </c>
       <c r="D74">
-        <v>-0.2087954808115853</v>
+        <v>-0.7896160779368091</v>
       </c>
       <c r="E74" t="s">
         <v>9</v>
@@ -1673,7 +1673,7 @@
         <v>4</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>-0.4999690282577852</v>
       </c>
       <c r="E75" t="s">
         <v>9</v>
@@ -1690,7 +1690,7 @@
         <v>4</v>
       </c>
       <c r="D76">
-        <v>-0.7497210432719079</v>
+        <v>-0.6621848762751285</v>
       </c>
       <c r="E76" t="s">
         <v>9</v>
@@ -1707,7 +1707,7 @@
         <v>4</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>-0.02216852767854142</v>
       </c>
       <c r="E77" t="s">
         <v>9</v>
@@ -1724,7 +1724,7 @@
         <v>4</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>-0.2609830704629769</v>
       </c>
       <c r="E78" t="s">
         <v>9</v>
@@ -1741,7 +1741,7 @@
         <v>4</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>-0.1135374654112868</v>
       </c>
       <c r="E79" t="s">
         <v>9</v>
@@ -1758,7 +1758,7 @@
         <v>4</v>
       </c>
       <c r="D80">
-        <v>-0.3237026277770468</v>
+        <v>0</v>
       </c>
       <c r="E80" t="s">
         <v>9</v>
@@ -1775,7 +1775,7 @@
         <v>4</v>
       </c>
       <c r="D81">
-        <v>-0.3450693672710372</v>
+        <v>-0.4029869885593761</v>
       </c>
       <c r="E81" t="s">
         <v>9</v>
@@ -1809,7 +1809,7 @@
         <v>4</v>
       </c>
       <c r="D83">
-        <v>-0.1433447182914055</v>
+        <v>-1.712749558933046</v>
       </c>
       <c r="E83" t="s">
         <v>9</v>
@@ -1826,7 +1826,7 @@
         <v>4</v>
       </c>
       <c r="D84">
-        <v>-0.2137004292506069</v>
+        <v>0</v>
       </c>
       <c r="E84" t="s">
         <v>9</v>
@@ -1843,7 +1843,7 @@
         <v>4</v>
       </c>
       <c r="D85">
-        <v>-1.46869796931746</v>
+        <v>-0.9419915795396504</v>
       </c>
       <c r="E85" t="s">
         <v>9</v>
@@ -1860,7 +1860,7 @@
         <v>4</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>-0.5095210258592329</v>
       </c>
       <c r="E86" t="s">
         <v>9</v>
@@ -1877,7 +1877,7 @@
         <v>4</v>
       </c>
       <c r="D87">
-        <v>-0.1398451982896312</v>
+        <v>-0.8520585113384365</v>
       </c>
       <c r="E87" t="s">
         <v>9</v>
@@ -1894,7 +1894,7 @@
         <v>4</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>-0.0977631613428397</v>
       </c>
       <c r="E88" t="s">
         <v>9</v>
@@ -1911,7 +1911,7 @@
         <v>4</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>-0.2503044766991406</v>
       </c>
       <c r="E89" t="s">
         <v>9</v>
@@ -1928,7 +1928,7 @@
         <v>4</v>
       </c>
       <c r="D90">
-        <v>-0.5146173227165936</v>
+        <v>-0.4252221285858109</v>
       </c>
       <c r="E90" t="s">
         <v>9</v>
@@ -1945,7 +1945,7 @@
         <v>4</v>
       </c>
       <c r="D91">
-        <v>-0.3609740974516575</v>
+        <v>-0.4230948899334148</v>
       </c>
       <c r="E91" t="s">
         <v>9</v>
@@ -1979,7 +1979,7 @@
         <v>5</v>
       </c>
       <c r="D93">
-        <v>-0.01801991369692839</v>
+        <v>-0.1947486212250789</v>
       </c>
       <c r="E93" t="s">
         <v>9</v>
@@ -2030,7 +2030,7 @@
         <v>5</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>-0.06419700381178048</v>
       </c>
       <c r="E96" t="s">
         <v>9</v>
@@ -2166,7 +2166,7 @@
         <v>5</v>
       </c>
       <c r="D104">
-        <v>-0.01667616014765217</v>
+        <v>-0.4608496593644127</v>
       </c>
       <c r="E104" t="s">
         <v>9</v>
@@ -2183,7 +2183,7 @@
         <v>5</v>
       </c>
       <c r="D105">
-        <v>-0.02179438330797836</v>
+        <v>-0.3055132275057899</v>
       </c>
       <c r="E105" t="s">
         <v>9</v>
@@ -2200,7 +2200,7 @@
         <v>5</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>-0.2278075908125561</v>
       </c>
       <c r="E106" t="s">
         <v>9</v>
@@ -2251,7 +2251,7 @@
         <v>5</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>-0.05346337918658972</v>
       </c>
       <c r="E109" t="s">
         <v>9</v>
@@ -2268,7 +2268,7 @@
         <v>6</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>-1.217570830448832</v>
       </c>
       <c r="E110" t="s">
         <v>9</v>
@@ -2285,7 +2285,7 @@
         <v>6</v>
       </c>
       <c r="D111">
-        <v>-8.126279537892605</v>
+        <v>-7.825821083942652</v>
       </c>
       <c r="E111" t="s">
         <v>9</v>
@@ -2302,7 +2302,7 @@
         <v>6</v>
       </c>
       <c r="D112">
-        <v>-2.328074945466622</v>
+        <v>-3.849363753235811</v>
       </c>
       <c r="E112" t="s">
         <v>9</v>
@@ -2319,7 +2319,7 @@
         <v>6</v>
       </c>
       <c r="D113">
-        <v>-8.276590009366021</v>
+        <v>-8.166028623957136</v>
       </c>
       <c r="E113" t="s">
         <v>9</v>
@@ -2336,7 +2336,7 @@
         <v>6</v>
       </c>
       <c r="D114">
-        <v>-3.344905385019417</v>
+        <v>-6.076891111325687</v>
       </c>
       <c r="E114" t="s">
         <v>9</v>
@@ -2353,7 +2353,7 @@
         <v>6</v>
       </c>
       <c r="D115">
-        <v>-1.941170782622454</v>
+        <v>-2.333313047891993</v>
       </c>
       <c r="E115" t="s">
         <v>9</v>
@@ -2370,7 +2370,7 @@
         <v>6</v>
       </c>
       <c r="D116">
-        <v>-4.641907340797494</v>
+        <v>-10.19508734804542</v>
       </c>
       <c r="E116" t="s">
         <v>9</v>
@@ -2387,7 +2387,7 @@
         <v>6</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>-0.7829581289253488</v>
       </c>
       <c r="E117" t="s">
         <v>9</v>
@@ -2404,7 +2404,7 @@
         <v>6</v>
       </c>
       <c r="D118">
-        <v>-1.196638312370011</v>
+        <v>-3.46780589956638</v>
       </c>
       <c r="E118" t="s">
         <v>9</v>
@@ -2421,7 +2421,7 @@
         <v>6</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>-0.2064594039612854</v>
       </c>
       <c r="E119" t="s">
         <v>9</v>
@@ -2438,7 +2438,7 @@
         <v>6</v>
       </c>
       <c r="D120">
-        <v>-0.7081712260856087</v>
+        <v>-5.342435222191184</v>
       </c>
       <c r="E120" t="s">
         <v>9</v>
@@ -2455,7 +2455,7 @@
         <v>6</v>
       </c>
       <c r="D121">
-        <v>-0.9496770388082161</v>
+        <v>-3.05985784692272</v>
       </c>
       <c r="E121" t="s">
         <v>9</v>
@@ -2472,7 +2472,7 @@
         <v>6</v>
       </c>
       <c r="D122">
-        <v>-0.7461659314738354</v>
+        <v>-6.206234348051954</v>
       </c>
       <c r="E122" t="s">
         <v>9</v>
@@ -2489,7 +2489,7 @@
         <v>6</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>-1.070041636771932</v>
       </c>
       <c r="E123" t="s">
         <v>9</v>
@@ -2506,7 +2506,7 @@
         <v>6</v>
       </c>
       <c r="D124">
-        <v>-6.40842354478549</v>
+        <v>-9.526794164893376</v>
       </c>
       <c r="E124" t="s">
         <v>9</v>
@@ -2523,7 +2523,7 @@
         <v>6</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>-0.1131326822018278</v>
       </c>
       <c r="E125" t="s">
         <v>9</v>
@@ -2540,7 +2540,7 @@
         <v>6</v>
       </c>
       <c r="D126">
-        <v>-0.0204583810373023</v>
+        <v>-0.3865586439271236</v>
       </c>
       <c r="E126" t="s">
         <v>9</v>
@@ -2557,7 +2557,7 @@
         <v>6</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>-0.2321888572437578</v>
       </c>
       <c r="E127" t="s">
         <v>9</v>
@@ -2574,7 +2574,7 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>-8.485385490177604</v>
+        <v>-7.843602119671194</v>
       </c>
       <c r="E128" t="s">
         <v>9</v>
@@ -2591,7 +2591,7 @@
         <v>7</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>-1.119379634444894</v>
       </c>
       <c r="E129" t="s">
         <v>9</v>
@@ -2608,7 +2608,7 @@
         <v>7</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>-0.3417601737040845</v>
       </c>
       <c r="E130" t="s">
         <v>9</v>
@@ -2625,7 +2625,7 @@
         <v>7</v>
       </c>
       <c r="D131">
-        <v>-0.7461659314738354</v>
+        <v>-5.899534004381418</v>
       </c>
       <c r="E131" t="s">
         <v>9</v>
@@ -2642,7 +2642,7 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>-1.326833201688916</v>
+        <v>-3.815010692239088</v>
       </c>
       <c r="E132" t="s">
         <v>9</v>
@@ -2659,7 +2659,7 @@
         <v>7</v>
       </c>
       <c r="D133">
-        <v>-8.321338022102017</v>
+        <v>-7.527312498422528</v>
       </c>
       <c r="E133" t="s">
         <v>9</v>
@@ -2676,7 +2676,7 @@
         <v>7</v>
       </c>
       <c r="D134">
-        <v>-3.344905385019417</v>
+        <v>-5.712589111712785</v>
       </c>
       <c r="E134" t="s">
         <v>9</v>
@@ -2693,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="D135">
-        <v>-4.785252059088899</v>
+        <v>-10.41078876414832</v>
       </c>
       <c r="E135" t="s">
         <v>9</v>
@@ -2710,7 +2710,7 @@
         <v>7</v>
       </c>
       <c r="D136">
-        <v>-0.3417225414739752</v>
+        <v>-0.3767053062691204</v>
       </c>
       <c r="E136" t="s">
         <v>9</v>
@@ -2727,7 +2727,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>-6.769397642237148</v>
+        <v>-9.123594258231615</v>
       </c>
       <c r="E137" t="s">
         <v>9</v>
@@ -2744,7 +2744,7 @@
         <v>7</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>-0.2978240966892922</v>
       </c>
       <c r="E138" t="s">
         <v>9</v>
@@ -2761,7 +2761,7 @@
         <v>7</v>
       </c>
       <c r="D139">
-        <v>-0.0204583810373023</v>
+        <v>-0.3553845597394524</v>
       </c>
       <c r="E139" t="s">
         <v>9</v>
@@ -2778,7 +2778,7 @@
         <v>7</v>
       </c>
       <c r="D140">
-        <v>-0.2303765893982591</v>
+        <v>-1.053933197539689</v>
       </c>
       <c r="E140" t="s">
         <v>9</v>
@@ -2795,7 +2795,7 @@
         <v>7</v>
       </c>
       <c r="D141">
-        <v>-0.7081712260856087</v>
+        <v>-5.343018559301435</v>
       </c>
       <c r="E141" t="s">
         <v>9</v>
@@ -2812,7 +2812,7 @@
         <v>7</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>-0.8070960785314211</v>
       </c>
       <c r="E142" t="s">
         <v>9</v>
@@ -2829,7 +2829,7 @@
         <v>7</v>
       </c>
       <c r="D143">
-        <v>-1.941170782622454</v>
+        <v>-2.345347175031115</v>
       </c>
       <c r="E143" t="s">
         <v>9</v>
@@ -2846,7 +2846,7 @@
         <v>7</v>
       </c>
       <c r="D144">
-        <v>-2.851118142791655</v>
+        <v>-3.993184537187247</v>
       </c>
       <c r="E144" t="s">
         <v>9</v>
@@ -2863,7 +2863,7 @@
         <v>7</v>
       </c>
       <c r="D145">
-        <v>-1.553791471757223</v>
+        <v>-3.207052609628726</v>
       </c>
       <c r="E145" t="s">
         <v>9</v>
@@ -2880,7 +2880,7 @@
         <v>4</v>
       </c>
       <c r="D146">
-        <v>-0.1665076770136946</v>
+        <v>-1.286365015388976</v>
       </c>
       <c r="E146" t="s">
         <v>10</v>
@@ -2897,7 +2897,7 @@
         <v>4</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>-0.474094239594676</v>
       </c>
       <c r="E147" t="s">
         <v>10</v>
@@ -2914,7 +2914,7 @@
         <v>4</v>
       </c>
       <c r="D148">
-        <v>-0.2435231427830179</v>
+        <v>-0.5488931043806552</v>
       </c>
       <c r="E148" t="s">
         <v>10</v>
@@ -2931,7 +2931,7 @@
         <v>4</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>-0.2957157554155594</v>
       </c>
       <c r="E149" t="s">
         <v>10</v>
@@ -2948,7 +2948,7 @@
         <v>4</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>-0.4348617339796584</v>
       </c>
       <c r="E150" t="s">
         <v>10</v>
@@ -2965,7 +2965,7 @@
         <v>4</v>
       </c>
       <c r="D151">
-        <v>-0.03030159848419754</v>
+        <v>-0.8434093369466404</v>
       </c>
       <c r="E151" t="s">
         <v>10</v>
@@ -2982,7 +2982,7 @@
         <v>4</v>
       </c>
       <c r="D152">
-        <v>-0.2231968599823196</v>
+        <v>-0.327965600014544</v>
       </c>
       <c r="E152" t="s">
         <v>10</v>
@@ -2999,7 +2999,7 @@
         <v>4</v>
       </c>
       <c r="D153">
-        <v>-1.312966207456929</v>
+        <v>-1.795463225739556</v>
       </c>
       <c r="E153" t="s">
         <v>10</v>
@@ -3016,7 +3016,7 @@
         <v>4</v>
       </c>
       <c r="D154">
-        <v>-0.1193699810409606</v>
+        <v>-0.1721965769466908</v>
       </c>
       <c r="E154" t="s">
         <v>10</v>
@@ -3033,7 +3033,7 @@
         <v>4</v>
       </c>
       <c r="D155">
-        <v>-0.07276758048395447</v>
+        <v>-1.367153535351535</v>
       </c>
       <c r="E155" t="s">
         <v>10</v>
@@ -3050,7 +3050,7 @@
         <v>4</v>
       </c>
       <c r="D156">
-        <v>-0.1179242462934501</v>
+        <v>-0.3444660762848705</v>
       </c>
       <c r="E156" t="s">
         <v>10</v>
@@ -3067,7 +3067,7 @@
         <v>4</v>
       </c>
       <c r="D157">
-        <v>-0.5490899741844123</v>
+        <v>-1.053559605219067</v>
       </c>
       <c r="E157" t="s">
         <v>10</v>
@@ -3084,7 +3084,7 @@
         <v>4</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>-0.6801584946071526</v>
       </c>
       <c r="E158" t="s">
         <v>10</v>
@@ -3101,7 +3101,7 @@
         <v>4</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>-0.8515982706261362</v>
       </c>
       <c r="E159" t="s">
         <v>10</v>
@@ -3118,7 +3118,7 @@
         <v>4</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>-0.3911744212204793</v>
       </c>
       <c r="E160" t="s">
         <v>10</v>
@@ -3135,7 +3135,7 @@
         <v>4</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>-0.4937977794252029</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
@@ -3152,7 +3152,7 @@
         <v>4</v>
       </c>
       <c r="D162">
-        <v>-0.7163319078271659</v>
+        <v>-0.8470716783148285</v>
       </c>
       <c r="E162" t="s">
         <v>10</v>
@@ -3169,7 +3169,7 @@
         <v>4</v>
       </c>
       <c r="D163">
-        <v>-0.08737580847272636</v>
+        <v>-1.127079098519584</v>
       </c>
       <c r="E163" t="s">
         <v>10</v>
@@ -3220,7 +3220,7 @@
         <v>5</v>
       </c>
       <c r="D166">
-        <v>-0.01676696330440616</v>
+        <v>-0.01780312395804924</v>
       </c>
       <c r="E166" t="s">
         <v>10</v>
@@ -3254,7 +3254,7 @@
         <v>5</v>
       </c>
       <c r="D168">
-        <v>-0.001791631004993741</v>
+        <v>0</v>
       </c>
       <c r="E168" t="s">
         <v>10</v>
@@ -3322,7 +3322,7 @@
         <v>5</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>-0.01992298473022137</v>
       </c>
       <c r="E172" t="s">
         <v>10</v>
@@ -3390,7 +3390,7 @@
         <v>5</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>-0.01082151763982062</v>
       </c>
       <c r="E176" t="s">
         <v>10</v>
@@ -3407,7 +3407,7 @@
         <v>5</v>
       </c>
       <c r="D177">
-        <v>-0.04726647265982347</v>
+        <v>-0.2449576417087691</v>
       </c>
       <c r="E177" t="s">
         <v>10</v>
@@ -3441,7 +3441,7 @@
         <v>5</v>
       </c>
       <c r="D179">
-        <v>-0.002246484475294376</v>
+        <v>0</v>
       </c>
       <c r="E179" t="s">
         <v>10</v>
@@ -3492,7 +3492,7 @@
         <v>6</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>-0.372342395371416</v>
       </c>
       <c r="E182" t="s">
         <v>10</v>
@@ -3509,7 +3509,7 @@
         <v>6</v>
       </c>
       <c r="D183">
-        <v>-1.320210607723436</v>
+        <v>-1.368885636758775</v>
       </c>
       <c r="E183" t="s">
         <v>10</v>
@@ -3526,7 +3526,7 @@
         <v>6</v>
       </c>
       <c r="D184">
-        <v>-0.9772271601703137</v>
+        <v>-1.453465590648675</v>
       </c>
       <c r="E184" t="s">
         <v>10</v>
@@ -3543,7 +3543,7 @@
         <v>6</v>
       </c>
       <c r="D185">
-        <v>-3.31541379394207</v>
+        <v>-2.637585505562241</v>
       </c>
       <c r="E185" t="s">
         <v>10</v>
@@ -3560,7 +3560,7 @@
         <v>6</v>
       </c>
       <c r="D186">
-        <v>-1.617980807293224</v>
+        <v>-2.429800977419472</v>
       </c>
       <c r="E186" t="s">
         <v>10</v>
@@ -3577,7 +3577,7 @@
         <v>6</v>
       </c>
       <c r="D187">
-        <v>-1.011488677048495</v>
+        <v>-0.4732166460783147</v>
       </c>
       <c r="E187" t="s">
         <v>10</v>
@@ -3594,7 +3594,7 @@
         <v>6</v>
       </c>
       <c r="D188">
-        <v>-1.907878884698577</v>
+        <v>-2.406483326552815</v>
       </c>
       <c r="E188" t="s">
         <v>10</v>
@@ -3628,7 +3628,7 @@
         <v>6</v>
       </c>
       <c r="D190">
-        <v>-0.531772663317113</v>
+        <v>-1.423306136586718</v>
       </c>
       <c r="E190" t="s">
         <v>10</v>
@@ -3662,7 +3662,7 @@
         <v>6</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>-0.8656254933442534</v>
       </c>
       <c r="E192" t="s">
         <v>10</v>
@@ -3679,7 +3679,7 @@
         <v>6</v>
       </c>
       <c r="D193">
-        <v>-0.1458830448447509</v>
+        <v>-0.3269687037235879</v>
       </c>
       <c r="E193" t="s">
         <v>10</v>
@@ -3696,7 +3696,7 @@
         <v>6</v>
       </c>
       <c r="D194">
-        <v>-0.04287681679660359</v>
+        <v>-1.208638831051047</v>
       </c>
       <c r="E194" t="s">
         <v>10</v>
@@ -3713,7 +3713,7 @@
         <v>6</v>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>-0.1374448112716828</v>
       </c>
       <c r="E195" t="s">
         <v>10</v>
@@ -3730,7 +3730,7 @@
         <v>6</v>
       </c>
       <c r="D196">
-        <v>-2.449391753664354</v>
+        <v>-2.23207646699174</v>
       </c>
       <c r="E196" t="s">
         <v>10</v>
@@ -3747,7 +3747,7 @@
         <v>6</v>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>-0.1044671918904221</v>
       </c>
       <c r="E197" t="s">
         <v>10</v>
@@ -3764,7 +3764,7 @@
         <v>6</v>
       </c>
       <c r="D198">
-        <v>-0.1306837315268894</v>
+        <v>-0.5669290950626903</v>
       </c>
       <c r="E198" t="s">
         <v>10</v>
@@ -3781,7 +3781,7 @@
         <v>6</v>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>-0.1532725199494076</v>
       </c>
       <c r="E199" t="s">
         <v>10</v>
@@ -3798,7 +3798,7 @@
         <v>7</v>
       </c>
       <c r="D200">
-        <v>-3.481921470955764</v>
+        <v>-3.254514926588657</v>
       </c>
       <c r="E200" t="s">
         <v>10</v>
@@ -3815,7 +3815,7 @@
         <v>7</v>
       </c>
       <c r="D201">
-        <v>-0.1193699810409606</v>
+        <v>-0.4689470951564512</v>
       </c>
       <c r="E201" t="s">
         <v>10</v>
@@ -3832,7 +3832,7 @@
         <v>7</v>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>-0.3401672924457828</v>
       </c>
       <c r="E202" t="s">
         <v>10</v>
@@ -3849,7 +3849,7 @@
         <v>7</v>
       </c>
       <c r="D203">
-        <v>-0.04287681679660359</v>
+        <v>-1.347551758576693</v>
       </c>
       <c r="E203" t="s">
         <v>10</v>
@@ -3866,7 +3866,7 @@
         <v>7</v>
       </c>
       <c r="D204">
-        <v>-0.531772663317113</v>
+        <v>-1.933071775323626</v>
       </c>
       <c r="E204" t="s">
         <v>10</v>
@@ -3883,7 +3883,7 @@
         <v>7</v>
       </c>
       <c r="D205">
-        <v>-2.036542515550602</v>
+        <v>-1.892735307162285</v>
       </c>
       <c r="E205" t="s">
         <v>10</v>
@@ -3900,7 +3900,7 @@
         <v>7</v>
       </c>
       <c r="D206">
-        <v>-1.617980807293224</v>
+        <v>-2.669496239395529</v>
       </c>
       <c r="E206" t="s">
         <v>10</v>
@@ -3917,7 +3917,7 @@
         <v>7</v>
       </c>
       <c r="D207">
-        <v>-1.982438096187525</v>
+        <v>-3.240450427283886</v>
       </c>
       <c r="E207" t="s">
         <v>10</v>
@@ -3934,7 +3934,7 @@
         <v>7</v>
       </c>
       <c r="D208">
-        <v>-0.2231968599823196</v>
+        <v>-0.2788584513492647</v>
       </c>
       <c r="E208" t="s">
         <v>10</v>
@@ -3951,7 +3951,7 @@
         <v>7</v>
       </c>
       <c r="D209">
-        <v>-2.536767562137081</v>
+        <v>-2.783636922416307</v>
       </c>
       <c r="E209" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>7</v>
       </c>
       <c r="D210">
-        <v>0</v>
+        <v>-0.4657613338165728</v>
       </c>
       <c r="E210" t="s">
         <v>10</v>
@@ -3985,7 +3985,7 @@
         <v>7</v>
       </c>
       <c r="D211">
-        <v>-0.1609853300110869</v>
+        <v>-1.193807048219637</v>
       </c>
       <c r="E211" t="s">
         <v>10</v>
@@ -4002,7 +4002,7 @@
         <v>7</v>
       </c>
       <c r="D212">
-        <v>-0.1179242462934501</v>
+        <v>-0.3707734591903682</v>
       </c>
       <c r="E212" t="s">
         <v>10</v>
@@ -4019,7 +4019,7 @@
         <v>7</v>
       </c>
       <c r="D213">
-        <v>-0.002246484475294376</v>
+        <v>-1.122600792024005</v>
       </c>
       <c r="E213" t="s">
         <v>10</v>
@@ -4036,7 +4036,7 @@
         <v>7</v>
       </c>
       <c r="D214">
-        <v>0</v>
+        <v>-0.3685718355071495</v>
       </c>
       <c r="E214" t="s">
         <v>10</v>
@@ -4053,7 +4053,7 @@
         <v>7</v>
       </c>
       <c r="D215">
-        <v>-2.324454884505424</v>
+        <v>-1.934928810554529</v>
       </c>
       <c r="E215" t="s">
         <v>10</v>
@@ -4070,7 +4070,7 @@
         <v>7</v>
       </c>
       <c r="D216">
-        <v>-1.30999779838602</v>
+        <v>-1.964918927721264</v>
       </c>
       <c r="E216" t="s">
         <v>10</v>
@@ -4087,7 +4087,7 @@
         <v>7</v>
       </c>
       <c r="D217">
-        <v>-0.260290106087424</v>
+        <v>-0.7120261234854208</v>
       </c>
       <c r="E217" t="s">
         <v>10</v>
